--- a/HORAS-EXTRAS- FEVEREIRO-2026.xlsx
+++ b/HORAS-EXTRAS- FEVEREIRO-2026.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projeto.dev\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB7470C-ED93-441D-8591-5F75620CB02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9917B0FA-4770-4EC1-A6DD-A8B698359DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7FAD56AE-9D28-4736-B635-37D3D3B1CDBF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Fev.2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fev.2026!$A$3:$F$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>HORAS EXTRAS ( FEVEREIRO / 2026 )</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>KAIK SILVA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FÁBIO DA SILVA CARVALHO</t>
+  </si>
+  <si>
+    <t>JARDIM DO MULATO</t>
   </si>
 </sst>
 </file>
@@ -238,7 +244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -270,11 +276,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -307,6 +322,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -649,10 +669,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31974592-B8CB-4C42-B44C-371B4698EC55}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="47.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
     <col min="2" max="2" width="53.85546875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="43.7109375" customWidth="1"/>
@@ -661,24 +681,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-    </row>
-    <row r="3" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" ht="42" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -751,12 +771,16 @@
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="C7" s="11">
+        <v>6020</v>
+      </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
@@ -1098,8 +1122,29 @@
       <c r="E29" s="4"/>
       <c r="F29" s="5"/>
     </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>27</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="10">
+        <v>6020</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C31" s="14"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F3" xr:uid="{31974592-B8CB-4C42-B44C-371B4698EC55}"/>
+  <autoFilter ref="A3:F29" xr:uid="{31974592-B8CB-4C42-B44C-371B4698EC55}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F2"/>
   </mergeCells>
